--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008439271833561955</v>
       </c>
       <c r="C2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>16575573</v>
+        <v>4189680</v>
       </c>
       <c r="L2" t="n">
-        <v>6302340</v>
+        <v>1533464</v>
       </c>
       <c r="M2" t="n">
-        <v>1145446</v>
+        <v>288230</v>
       </c>
       <c r="N2" t="n">
-        <v>25610</v>
+        <v>6476</v>
       </c>
       <c r="O2" t="n">
-        <v>698921</v>
+        <v>174434</v>
       </c>
       <c r="P2" t="n">
-        <v>14819</v>
+        <v>3470</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998970031738281</v>
+        <v>0.9998848438262939</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7189990878105164</v>
+        <v>0.7136304378509521</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5333613157272339</v>
+        <v>0.5379022359848022</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4010068476200104</v>
+        <v>0.402293473482132</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04508715495467186</v>
+        <v>0.04619741439819336</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4024032950401306</v>
+        <v>0.4056831002235413</v>
       </c>
       <c r="W2" t="n">
-        <v>0.454013466835022</v>
+        <v>0.462050586938858</v>
       </c>
       <c r="X2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25251912</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="AG2" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AH2" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AI2" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566228985786438</v>
+        <v>0.956451416015625</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112591743469238</v>
+        <v>0.9113048315048218</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.858102023601532</v>
+        <v>0.8578755855560303</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624639630317688</v>
+        <v>0.6619618535041809</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020282030105591</v>
+        <v>0.9019733667373657</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002023734838753813</v>
       </c>
       <c r="C3" t="n">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c r="D3" t="n">
-        <v>16575573</v>
+        <v>4189680</v>
       </c>
       <c r="E3" t="n">
-        <v>3373389</v>
+        <v>791167</v>
       </c>
       <c r="F3" t="n">
-        <v>145023</v>
+        <v>35414</v>
       </c>
       <c r="G3" t="n">
-        <v>16343</v>
+        <v>3843</v>
       </c>
       <c r="H3" t="n">
-        <v>13783</v>
+        <v>2908</v>
       </c>
       <c r="I3" t="n">
-        <v>639</v>
+        <v>136</v>
       </c>
       <c r="J3" t="n">
-        <v>40063887</v>
+        <v>10015895</v>
       </c>
       <c r="K3" t="n">
-        <v>38715329</v>
+        <v>9625113</v>
       </c>
       <c r="L3" t="n">
-        <v>46756724</v>
+        <v>11743354</v>
       </c>
       <c r="M3" t="n">
-        <v>59879544</v>
+        <v>14968772</v>
       </c>
       <c r="N3" t="n">
-        <v>64419610</v>
+        <v>16106704</v>
       </c>
       <c r="O3" t="n">
-        <v>62244140</v>
+        <v>15564680</v>
       </c>
       <c r="P3" t="n">
-        <v>64527387</v>
+        <v>16132214</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8236322999000549</v>
+        <v>0.8340611457824707</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4830212593078613</v>
+        <v>0.469108909368515</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3072649538516998</v>
+        <v>0.3090636730194092</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07185968011617661</v>
+        <v>0.07260822504758835</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3432284891605377</v>
+        <v>0.3424451053142548</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01916600205004215</v>
+        <v>0.01794710010290146</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19271788</v>
+        <v>4809709</v>
       </c>
       <c r="Z3" t="n">
-        <v>791602</v>
+        <v>198076</v>
       </c>
       <c r="AA3" t="n">
-        <v>34131</v>
+        <v>8559</v>
       </c>
       <c r="AB3" t="n">
-        <v>27146</v>
+        <v>6810</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40066488</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>44319573</v>
+        <v>11087378</v>
       </c>
       <c r="AG3" t="n">
-        <v>51114353</v>
+        <v>12771195</v>
       </c>
       <c r="AH3" t="n">
-        <v>61061800</v>
+        <v>15264532</v>
       </c>
       <c r="AI3" t="n">
-        <v>64841808</v>
+        <v>16210280</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63082667</v>
+        <v>15770309</v>
       </c>
       <c r="AK3" t="n">
-        <v>64492192</v>
+        <v>16123000</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576059579849243</v>
+        <v>0.9574934840202332</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100238084793091</v>
+        <v>0.909995973110199</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576881885528564</v>
+        <v>0.857442319393158</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66196209192276</v>
+        <v>0.6615017056465149</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016556143760681</v>
+        <v>0.9016192555427551</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03193050064849949</v>
       </c>
       <c r="C4" t="n">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>5755725</v>
+        <v>1491177</v>
       </c>
       <c r="E4" t="n">
-        <v>6302340</v>
+        <v>1533464</v>
       </c>
       <c r="F4" t="n">
-        <v>766266</v>
+        <v>190516</v>
       </c>
       <c r="G4" t="n">
-        <v>88141</v>
+        <v>21470</v>
       </c>
       <c r="H4" t="n">
-        <v>132682</v>
+        <v>31697</v>
       </c>
       <c r="I4" t="n">
-        <v>2497</v>
+        <v>526</v>
       </c>
       <c r="J4" t="n">
-        <v>2601</v>
+        <v>727</v>
       </c>
       <c r="K4" t="n">
-        <v>6478104</v>
+        <v>1681258</v>
       </c>
       <c r="L4" t="n">
-        <v>5513927</v>
+        <v>1317359</v>
       </c>
       <c r="M4" t="n">
-        <v>1710979</v>
+        <v>428237</v>
       </c>
       <c r="N4" t="n">
-        <v>542401</v>
+        <v>133705</v>
       </c>
       <c r="O4" t="n">
-        <v>1037946</v>
+        <v>255542</v>
       </c>
       <c r="P4" t="n">
-        <v>17821</v>
+        <v>4040</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999485015869141</v>
+        <v>0.999942421913147</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7677671909332275</v>
+        <v>0.769160270690918</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5069446563720703</v>
+        <v>0.5011557936668396</v>
       </c>
       <c r="T4" t="n">
-        <v>0.347932368516922</v>
+        <v>0.3495692908763885</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05540891364216805</v>
+        <v>0.05646722018718719</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3704677522182465</v>
+        <v>0.3713914155960083</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03677937760949135</v>
+        <v>0.03455211594700813</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>815845</v>
+        <v>204447</v>
       </c>
       <c r="Z4" t="n">
-        <v>11873762</v>
+        <v>2974674</v>
       </c>
       <c r="AA4" t="n">
-        <v>331353</v>
+        <v>83051</v>
       </c>
       <c r="AB4" t="n">
-        <v>21937</v>
+        <v>5499</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>873860</v>
+        <v>218993</v>
       </c>
       <c r="AG4" t="n">
-        <v>1156298</v>
+        <v>289518</v>
       </c>
       <c r="AH4" t="n">
-        <v>528723</v>
+        <v>132477</v>
       </c>
       <c r="AI4" t="n">
-        <v>120203</v>
+        <v>30129</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199419</v>
+        <v>49913</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571141600608826</v>
+        <v>0.9569721221923828</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910641074180603</v>
+        <v>0.9106499552726746</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578950166702271</v>
+        <v>0.857658863067627</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622129082679749</v>
+        <v>0.6617317199707031</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018418788909912</v>
+        <v>0.9017962217330933</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>330</v>
+        <v>92</v>
       </c>
       <c r="D5" t="n">
-        <v>534232</v>
+        <v>140509</v>
       </c>
       <c r="E5" t="n">
-        <v>1585844</v>
+        <v>389883</v>
       </c>
       <c r="F5" t="n">
-        <v>1145446</v>
+        <v>288230</v>
       </c>
       <c r="G5" t="n">
-        <v>140355</v>
+        <v>35147</v>
       </c>
       <c r="H5" t="n">
-        <v>317396</v>
+        <v>77693</v>
       </c>
       <c r="I5" t="n">
-        <v>4274</v>
+        <v>1037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3549394</v>
+        <v>833549</v>
       </c>
       <c r="L5" t="n">
-        <v>6745409</v>
+        <v>1735423</v>
       </c>
       <c r="M5" t="n">
-        <v>2582431</v>
+        <v>644361</v>
       </c>
       <c r="N5" t="n">
-        <v>330779</v>
+        <v>82715</v>
       </c>
       <c r="O5" t="n">
-        <v>1337393</v>
+        <v>334944</v>
       </c>
       <c r="P5" t="n">
-        <v>758373</v>
+        <v>189876</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.99996018409729</v>
+        <v>0.9999554753303528</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8464828133583069</v>
+        <v>0.8459970355033875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8123142123222351</v>
+        <v>0.813052237033844</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9342694878578186</v>
+        <v>0.9343157410621643</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9866319298744202</v>
+        <v>0.9867467880249023</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9636344313621521</v>
+        <v>0.9638395309448242</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9881167411804199</v>
+        <v>0.9881249070167542</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32012</v>
+        <v>8028</v>
       </c>
       <c r="Z5" t="n">
-        <v>339750</v>
+        <v>85185</v>
       </c>
       <c r="AA5" t="n">
-        <v>3197356</v>
+        <v>799643</v>
       </c>
       <c r="AB5" t="n">
-        <v>39755</v>
+        <v>9960</v>
       </c>
       <c r="AC5" t="n">
-        <v>116472</v>
+        <v>29142</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>853179</v>
+        <v>213520</v>
       </c>
       <c r="AG5" t="n">
-        <v>1173987</v>
+        <v>294213</v>
       </c>
       <c r="AH5" t="n">
-        <v>530521</v>
+        <v>132948</v>
       </c>
       <c r="AI5" t="n">
-        <v>120473</v>
+        <v>30191</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200260</v>
+        <v>50113</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735596776008606</v>
+        <v>0.9735135436058044</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643242359161377</v>
+        <v>0.9642531871795654</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837833642959595</v>
+        <v>0.9837457537651062</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963153600692749</v>
+        <v>0.9963061213493347</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938810467720032</v>
+        <v>0.9938745498657227</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998375415802002</v>
+        <v>0.9983739256858826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>196</v>
+        <v>57</v>
       </c>
       <c r="D6" t="n">
-        <v>95528</v>
+        <v>24940</v>
       </c>
       <c r="E6" t="n">
-        <v>105096</v>
+        <v>25463</v>
       </c>
       <c r="F6" t="n">
-        <v>95498</v>
+        <v>23825</v>
       </c>
       <c r="G6" t="n">
-        <v>25610</v>
+        <v>6476</v>
       </c>
       <c r="H6" t="n">
-        <v>33437</v>
+        <v>8201</v>
       </c>
       <c r="I6" t="n">
-        <v>1024</v>
+        <v>229</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25780</v>
+        <v>6462</v>
       </c>
       <c r="Z6" t="n">
-        <v>21382</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>43482</v>
+        <v>10898</v>
       </c>
       <c r="AB6" t="n">
-        <v>235916</v>
+        <v>59000</v>
       </c>
       <c r="AC6" t="n">
-        <v>27905</v>
+        <v>6984</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>802</v>
+        <v>219</v>
       </c>
       <c r="D7" t="n">
-        <v>84735</v>
+        <v>22469</v>
       </c>
       <c r="E7" t="n">
-        <v>400254</v>
+        <v>98625</v>
       </c>
       <c r="F7" t="n">
-        <v>601641</v>
+        <v>152444</v>
       </c>
       <c r="G7" t="n">
-        <v>240574</v>
+        <v>59075</v>
       </c>
       <c r="H7" t="n">
-        <v>698921</v>
+        <v>174434</v>
       </c>
       <c r="I7" t="n">
-        <v>9387</v>
+        <v>2112</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3240</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118437</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30304</v>
+        <v>7594</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836054</v>
+        <v>459265</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>958</v>
+        <v>241</v>
       </c>
       <c r="D8" t="n">
-        <v>7884</v>
+        <v>2163</v>
       </c>
       <c r="E8" t="n">
-        <v>49344</v>
+        <v>12221</v>
       </c>
       <c r="F8" t="n">
-        <v>102551</v>
+        <v>26038</v>
       </c>
       <c r="G8" t="n">
-        <v>56988</v>
+        <v>14170</v>
       </c>
       <c r="H8" t="n">
-        <v>540648</v>
+        <v>135043</v>
       </c>
       <c r="I8" t="n">
-        <v>14819</v>
+        <v>3470</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
